--- a/outputs/scenario_campaigns_20260716/03_rsa_staging_artifact.xlsx
+++ b/outputs/scenario_campaigns_20260716/03_rsa_staging_artifact.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="R707c2a9537fc4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="R093f2de0eea9456e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -427,7 +427,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K2" t="str">
         <x:v>{KeyWord:Critical Site C-UAS}</x:v>
@@ -466,7 +466,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Security</x:v>
       </x:c>
       <x:c r="W2" t="str">
-        <x:v>{KeyWord:Critical Site C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Critical Site C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X2" t="str">
         <x:v>{KeyWord:Critical Site C-UAS} Detection</x:v>
@@ -475,7 +475,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z2" t="str">
-        <x:v>Use {KeyWord:Critical Site C-UAS} to monitor critical assets and unauthorized aerial activity.</x:v>
+        <x:v>Deploy {KeyWord:Critical Site C-UAS} for critical facilities and national asset security.</x:v>
       </x:c>
       <x:c r="AA2" t="str">
         <x:v>Plan {KeyWord:Critical Site C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -542,7 +542,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K3" t="str">
         <x:v>{KeyWord:Power Plant C-UAS}</x:v>
@@ -581,7 +581,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Security</x:v>
       </x:c>
       <x:c r="W3" t="str">
-        <x:v>{KeyWord:Power Plant C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Power Plant C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X3" t="str">
         <x:v>{KeyWord:Power Plant C-UAS} Detection</x:v>
@@ -590,7 +590,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z3" t="str">
-        <x:v>Use {KeyWord:Power Plant C-UAS} to monitor power plants, grids and energy sites.</x:v>
+        <x:v>Deploy {KeyWord:Power Plant C-UAS} for power plants, grids and energy site security.</x:v>
       </x:c>
       <x:c r="AA3" t="str">
         <x:v>Plan {KeyWord:Power Plant C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -657,7 +657,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K4" t="str">
         <x:v>{KeyWord:Airport C-UAS}</x:v>
@@ -696,7 +696,7 @@
         <x:v>{KeyWord:Airport C-UAS} Security</x:v>
       </x:c>
       <x:c r="W4" t="str">
-        <x:v>{KeyWord:Airport C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Airport C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X4" t="str">
         <x:v>{KeyWord:Airport C-UAS} Detection</x:v>
@@ -705,7 +705,7 @@
         <x:v>{KeyWord:Airport C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z4" t="str">
-        <x:v>Use {KeyWord:Airport C-UAS} to monitor drone risks near runways and flight operations.</x:v>
+        <x:v>Deploy {KeyWord:Airport C-UAS} for runways, airfields and airport security.</x:v>
       </x:c>
       <x:c r="AA4" t="str">
         <x:v>Plan {KeyWord:Airport C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -772,7 +772,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K5" t="str">
         <x:v>{KeyWord:Border C-UAS}</x:v>
@@ -811,7 +811,7 @@
         <x:v>{KeyWord:Border C-UAS} Security</x:v>
       </x:c>
       <x:c r="W5" t="str">
-        <x:v>{KeyWord:Border C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Border C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X5" t="str">
         <x:v>{KeyWord:Border C-UAS} Detection</x:v>
@@ -820,7 +820,7 @@
         <x:v>{KeyWord:Border C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z5" t="str">
-        <x:v>Use {KeyWord:Border C-UAS} to monitor border posts, patrol routes and unauthorized drones.</x:v>
+        <x:v>Deploy {KeyWord:Border C-UAS} for border posts, checkpoints and patrol routes.</x:v>
       </x:c>
       <x:c r="AA5" t="str">
         <x:v>Plan {KeyWord:Border C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -887,7 +887,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K6" t="str">
         <x:v>{KeyWord:Public Safety C-UAS}</x:v>
@@ -926,7 +926,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Security</x:v>
       </x:c>
       <x:c r="W6" t="str">
-        <x:v>{KeyWord:Public Safety C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Public Safety C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X6" t="str">
         <x:v>{KeyWord:Public Safety C-UAS} Detection</x:v>
@@ -935,7 +935,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z6" t="str">
-        <x:v>Use {KeyWord:Public Safety C-UAS} for law enforcement, urban events and emergency deployment.</x:v>
+        <x:v>Deploy {KeyWord:Public Safety C-UAS} for police, urban security and emergency response.</x:v>
       </x:c>
       <x:c r="AA6" t="str">
         <x:v>Plan {KeyWord:Public Safety C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1002,7 +1002,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K7" t="str">
         <x:v>{KeyWord:Prison C-UAS}</x:v>
@@ -1041,7 +1041,7 @@
         <x:v>{KeyWord:Prison C-UAS} Security</x:v>
       </x:c>
       <x:c r="W7" t="str">
-        <x:v>{KeyWord:Prison C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Prison C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X7" t="str">
         <x:v>{KeyWord:Prison C-UAS} Detection</x:v>
@@ -1050,7 +1050,7 @@
         <x:v>{KeyWord:Prison C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z7" t="str">
-        <x:v>Use {KeyWord:Prison C-UAS} to detect contraband delivery risks and perimeter intrusion.</x:v>
+        <x:v>Deploy {KeyWord:Prison C-UAS} for prison perimeter and contraband drone detection.</x:v>
       </x:c>
       <x:c r="AA7" t="str">
         <x:v>Plan {KeyWord:Prison C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1117,7 +1117,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K8" t="str">
         <x:v>{KeyWord:Port Security C-UAS}</x:v>
@@ -1156,7 +1156,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Security</x:v>
       </x:c>
       <x:c r="W8" t="str">
-        <x:v>{KeyWord:Port Security C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Port Security C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X8" t="str">
         <x:v>{KeyWord:Port Security C-UAS} Detection</x:v>
@@ -1165,7 +1165,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z8" t="str">
-        <x:v>Use {KeyWord:Port Security C-UAS} to monitor cargo, logistics and unauthorized aerial surveillance.</x:v>
+        <x:v>Deploy {KeyWord:Port Security C-UAS} for ports, cargo terminals and logistics security.</x:v>
       </x:c>
       <x:c r="AA8" t="str">
         <x:v>Plan {KeyWord:Port Security C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1199,7 +1199,7 @@
         <x:v>port-security</x:v>
       </x:c>
       <x:c r="AX8" t="str">
-        <x:v>drone-monitor</x:v>
+        <x:v>drone-system</x:v>
       </x:c>
       <x:c r="AY8" t="str">
         <x:v>https://n-tet.com/solutions/low-altitude-airspace-monitoring</x:v>
@@ -1232,7 +1232,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K9" t="str">
         <x:v>{KeyWord:Mass Event C-UAS}</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Security</x:v>
       </x:c>
       <x:c r="W9" t="str">
-        <x:v>{KeyWord:Mass Event C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Mass Event C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X9" t="str">
         <x:v>{KeyWord:Mass Event C-UAS} Detection</x:v>
@@ -1280,7 +1280,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z9" t="str">
-        <x:v>Use {KeyWord:Mass Event C-UAS} to monitor stadiums, major events and dense crowds.</x:v>
+        <x:v>Deploy {KeyWord:Mass Event C-UAS} for stadiums, concerts and major event security.</x:v>
       </x:c>
       <x:c r="AA9" t="str">
         <x:v>Plan {KeyWord:Mass Event C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1347,7 +1347,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K10" t="str">
         <x:v>{KeyWord:VIP Property C-UAS}</x:v>
@@ -1386,7 +1386,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Security</x:v>
       </x:c>
       <x:c r="W10" t="str">
-        <x:v>{KeyWord:VIP Property C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:VIP Property C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X10" t="str">
         <x:v>{KeyWord:VIP Property C-UAS} Detection</x:v>
@@ -1395,7 +1395,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z10" t="str">
-        <x:v>Use {KeyWord:VIP Property C-UAS} for convoys, residences and private asset protection.</x:v>
+        <x:v>Deploy {KeyWord:VIP Property C-UAS} for villas, convoys and private estate security.</x:v>
       </x:c>
       <x:c r="AA10" t="str">
         <x:v>Plan {KeyWord:VIP Property C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1462,7 +1462,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K11" t="str">
         <x:v>{KeyWord:Enterprise C-UAS}</x:v>
@@ -1501,7 +1501,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Security</x:v>
       </x:c>
       <x:c r="W11" t="str">
-        <x:v>{KeyWord:Enterprise C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Enterprise C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X11" t="str">
         <x:v>{KeyWord:Enterprise C-UAS} Detection</x:v>
@@ -1510,7 +1510,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z11" t="str">
-        <x:v>Use {KeyWord:Enterprise C-UAS} to monitor headquarters, IP assets and unauthorized filming.</x:v>
+        <x:v>Deploy {KeyWord:Enterprise C-UAS} for mines, refineries and industrial site security.</x:v>
       </x:c>
       <x:c r="AA11" t="str">
         <x:v>Plan {KeyWord:Enterprise C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K12" t="str">
         <x:v>{KeyWord:Critical Site C-UAS}</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Security</x:v>
       </x:c>
       <x:c r="W12" t="str">
-        <x:v>{KeyWord:Critical Site C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Critical Site C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X12" t="str">
         <x:v>{KeyWord:Critical Site C-UAS} Detection</x:v>
@@ -1625,7 +1625,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:v>Use {KeyWord:Critical Site C-UAS} to monitor critical assets and unauthorized aerial activity.</x:v>
+        <x:v>Deploy {KeyWord:Critical Site C-UAS} for critical facilities and national asset security.</x:v>
       </x:c>
       <x:c r="AA12" t="str">
         <x:v>Plan {KeyWord:Critical Site C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1692,7 +1692,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K13" t="str">
         <x:v>{KeyWord:Power Plant C-UAS}</x:v>
@@ -1731,7 +1731,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Security</x:v>
       </x:c>
       <x:c r="W13" t="str">
-        <x:v>{KeyWord:Power Plant C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Power Plant C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X13" t="str">
         <x:v>{KeyWord:Power Plant C-UAS} Detection</x:v>
@@ -1740,7 +1740,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z13" t="str">
-        <x:v>Use {KeyWord:Power Plant C-UAS} to monitor power plants, grids and energy sites.</x:v>
+        <x:v>Deploy {KeyWord:Power Plant C-UAS} for power plants, grids and energy site security.</x:v>
       </x:c>
       <x:c r="AA13" t="str">
         <x:v>Plan {KeyWord:Power Plant C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1807,7 +1807,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K14" t="str">
         <x:v>{KeyWord:Airport C-UAS}</x:v>
@@ -1846,7 +1846,7 @@
         <x:v>{KeyWord:Airport C-UAS} Security</x:v>
       </x:c>
       <x:c r="W14" t="str">
-        <x:v>{KeyWord:Airport C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Airport C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X14" t="str">
         <x:v>{KeyWord:Airport C-UAS} Detection</x:v>
@@ -1855,7 +1855,7 @@
         <x:v>{KeyWord:Airport C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z14" t="str">
-        <x:v>Use {KeyWord:Airport C-UAS} to monitor drone risks near runways and flight operations.</x:v>
+        <x:v>Deploy {KeyWord:Airport C-UAS} for runways, airfields and airport security.</x:v>
       </x:c>
       <x:c r="AA14" t="str">
         <x:v>Plan {KeyWord:Airport C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -1922,7 +1922,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K15" t="str">
         <x:v>{KeyWord:Border C-UAS}</x:v>
@@ -1961,7 +1961,7 @@
         <x:v>{KeyWord:Border C-UAS} Security</x:v>
       </x:c>
       <x:c r="W15" t="str">
-        <x:v>{KeyWord:Border C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Border C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X15" t="str">
         <x:v>{KeyWord:Border C-UAS} Detection</x:v>
@@ -1970,7 +1970,7 @@
         <x:v>{KeyWord:Border C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z15" t="str">
-        <x:v>Use {KeyWord:Border C-UAS} to monitor border posts, patrol routes and unauthorized drones.</x:v>
+        <x:v>Deploy {KeyWord:Border C-UAS} for border posts, checkpoints and patrol routes.</x:v>
       </x:c>
       <x:c r="AA15" t="str">
         <x:v>Plan {KeyWord:Border C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2037,7 +2037,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K16" t="str">
         <x:v>{KeyWord:Public Safety C-UAS}</x:v>
@@ -2076,7 +2076,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Security</x:v>
       </x:c>
       <x:c r="W16" t="str">
-        <x:v>{KeyWord:Public Safety C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Public Safety C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X16" t="str">
         <x:v>{KeyWord:Public Safety C-UAS} Detection</x:v>
@@ -2085,7 +2085,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z16" t="str">
-        <x:v>Use {KeyWord:Public Safety C-UAS} for law enforcement, urban events and emergency deployment.</x:v>
+        <x:v>Deploy {KeyWord:Public Safety C-UAS} for police, urban security and emergency response.</x:v>
       </x:c>
       <x:c r="AA16" t="str">
         <x:v>Plan {KeyWord:Public Safety C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2152,7 +2152,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K17" t="str">
         <x:v>{KeyWord:Prison C-UAS}</x:v>
@@ -2191,7 +2191,7 @@
         <x:v>{KeyWord:Prison C-UAS} Security</x:v>
       </x:c>
       <x:c r="W17" t="str">
-        <x:v>{KeyWord:Prison C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Prison C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X17" t="str">
         <x:v>{KeyWord:Prison C-UAS} Detection</x:v>
@@ -2200,7 +2200,7 @@
         <x:v>{KeyWord:Prison C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z17" t="str">
-        <x:v>Use {KeyWord:Prison C-UAS} to detect contraband delivery risks and perimeter intrusion.</x:v>
+        <x:v>Deploy {KeyWord:Prison C-UAS} for prison perimeter and contraband drone detection.</x:v>
       </x:c>
       <x:c r="AA17" t="str">
         <x:v>Plan {KeyWord:Prison C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2267,7 +2267,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K18" t="str">
         <x:v>{KeyWord:Port Security C-UAS}</x:v>
@@ -2306,7 +2306,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Security</x:v>
       </x:c>
       <x:c r="W18" t="str">
-        <x:v>{KeyWord:Port Security C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Port Security C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X18" t="str">
         <x:v>{KeyWord:Port Security C-UAS} Detection</x:v>
@@ -2315,7 +2315,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z18" t="str">
-        <x:v>Use {KeyWord:Port Security C-UAS} to monitor cargo, logistics and unauthorized aerial surveillance.</x:v>
+        <x:v>Deploy {KeyWord:Port Security C-UAS} for ports, cargo terminals and logistics security.</x:v>
       </x:c>
       <x:c r="AA18" t="str">
         <x:v>Plan {KeyWord:Port Security C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2349,7 +2349,7 @@
         <x:v>port-security</x:v>
       </x:c>
       <x:c r="AX18" t="str">
-        <x:v>drone-monitor</x:v>
+        <x:v>drone-system</x:v>
       </x:c>
       <x:c r="AY18" t="str">
         <x:v>https://n-tet.com/solutions/low-altitude-airspace-monitoring</x:v>
@@ -2382,7 +2382,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K19" t="str">
         <x:v>{KeyWord:Mass Event C-UAS}</x:v>
@@ -2421,7 +2421,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Security</x:v>
       </x:c>
       <x:c r="W19" t="str">
-        <x:v>{KeyWord:Mass Event C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Mass Event C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X19" t="str">
         <x:v>{KeyWord:Mass Event C-UAS} Detection</x:v>
@@ -2430,7 +2430,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z19" t="str">
-        <x:v>Use {KeyWord:Mass Event C-UAS} to monitor stadiums, major events and dense crowds.</x:v>
+        <x:v>Deploy {KeyWord:Mass Event C-UAS} for stadiums, concerts and major event security.</x:v>
       </x:c>
       <x:c r="AA19" t="str">
         <x:v>Plan {KeyWord:Mass Event C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2497,7 +2497,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K20" t="str">
         <x:v>{KeyWord:VIP Property C-UAS}</x:v>
@@ -2536,7 +2536,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Security</x:v>
       </x:c>
       <x:c r="W20" t="str">
-        <x:v>{KeyWord:VIP Property C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:VIP Property C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X20" t="str">
         <x:v>{KeyWord:VIP Property C-UAS} Detection</x:v>
@@ -2545,7 +2545,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z20" t="str">
-        <x:v>Use {KeyWord:VIP Property C-UAS} for convoys, residences and private asset protection.</x:v>
+        <x:v>Deploy {KeyWord:VIP Property C-UAS} for villas, convoys and private estate security.</x:v>
       </x:c>
       <x:c r="AA20" t="str">
         <x:v>Plan {KeyWord:VIP Property C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2612,7 +2612,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K21" t="str">
         <x:v>{KeyWord:Enterprise C-UAS}</x:v>
@@ -2651,7 +2651,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Security</x:v>
       </x:c>
       <x:c r="W21" t="str">
-        <x:v>{KeyWord:Enterprise C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Enterprise C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X21" t="str">
         <x:v>{KeyWord:Enterprise C-UAS} Detection</x:v>
@@ -2660,7 +2660,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z21" t="str">
-        <x:v>Use {KeyWord:Enterprise C-UAS} to monitor headquarters, IP assets and unauthorized filming.</x:v>
+        <x:v>Deploy {KeyWord:Enterprise C-UAS} for mines, refineries and industrial site security.</x:v>
       </x:c>
       <x:c r="AA21" t="str">
         <x:v>Plan {KeyWord:Enterprise C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2727,7 +2727,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K22" t="str">
         <x:v>{KeyWord:Critical Site C-UAS}</x:v>
@@ -2766,7 +2766,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Security</x:v>
       </x:c>
       <x:c r="W22" t="str">
-        <x:v>{KeyWord:Critical Site C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Critical Site C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X22" t="str">
         <x:v>{KeyWord:Critical Site C-UAS} Detection</x:v>
@@ -2775,7 +2775,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z22" t="str">
-        <x:v>Use {KeyWord:Critical Site C-UAS} to monitor critical assets and unauthorized aerial activity.</x:v>
+        <x:v>Deploy {KeyWord:Critical Site C-UAS} for critical facilities and national asset security.</x:v>
       </x:c>
       <x:c r="AA22" t="str">
         <x:v>Plan {KeyWord:Critical Site C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2842,7 +2842,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K23" t="str">
         <x:v>{KeyWord:Power Plant C-UAS}</x:v>
@@ -2881,7 +2881,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Security</x:v>
       </x:c>
       <x:c r="W23" t="str">
-        <x:v>{KeyWord:Power Plant C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Power Plant C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X23" t="str">
         <x:v>{KeyWord:Power Plant C-UAS} Detection</x:v>
@@ -2890,7 +2890,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z23" t="str">
-        <x:v>Use {KeyWord:Power Plant C-UAS} to monitor power plants, grids and energy sites.</x:v>
+        <x:v>Deploy {KeyWord:Power Plant C-UAS} for power plants, grids and energy site security.</x:v>
       </x:c>
       <x:c r="AA23" t="str">
         <x:v>Plan {KeyWord:Power Plant C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -2957,7 +2957,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K24" t="str">
         <x:v>{KeyWord:Airport C-UAS}</x:v>
@@ -2996,7 +2996,7 @@
         <x:v>{KeyWord:Airport C-UAS} Security</x:v>
       </x:c>
       <x:c r="W24" t="str">
-        <x:v>{KeyWord:Airport C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Airport C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X24" t="str">
         <x:v>{KeyWord:Airport C-UAS} Detection</x:v>
@@ -3005,7 +3005,7 @@
         <x:v>{KeyWord:Airport C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z24" t="str">
-        <x:v>Use {KeyWord:Airport C-UAS} to monitor drone risks near runways and flight operations.</x:v>
+        <x:v>Deploy {KeyWord:Airport C-UAS} for runways, airfields and airport security.</x:v>
       </x:c>
       <x:c r="AA24" t="str">
         <x:v>Plan {KeyWord:Airport C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3072,7 +3072,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K25" t="str">
         <x:v>{KeyWord:Border C-UAS}</x:v>
@@ -3111,7 +3111,7 @@
         <x:v>{KeyWord:Border C-UAS} Security</x:v>
       </x:c>
       <x:c r="W25" t="str">
-        <x:v>{KeyWord:Border C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Border C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X25" t="str">
         <x:v>{KeyWord:Border C-UAS} Detection</x:v>
@@ -3120,7 +3120,7 @@
         <x:v>{KeyWord:Border C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z25" t="str">
-        <x:v>Use {KeyWord:Border C-UAS} to monitor border posts, patrol routes and unauthorized drones.</x:v>
+        <x:v>Deploy {KeyWord:Border C-UAS} for border posts, checkpoints and patrol routes.</x:v>
       </x:c>
       <x:c r="AA25" t="str">
         <x:v>Plan {KeyWord:Border C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3187,7 +3187,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K26" t="str">
         <x:v>{KeyWord:Public Safety C-UAS}</x:v>
@@ -3226,7 +3226,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Security</x:v>
       </x:c>
       <x:c r="W26" t="str">
-        <x:v>{KeyWord:Public Safety C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Public Safety C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X26" t="str">
         <x:v>{KeyWord:Public Safety C-UAS} Detection</x:v>
@@ -3235,7 +3235,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z26" t="str">
-        <x:v>Use {KeyWord:Public Safety C-UAS} for law enforcement, urban events and emergency deployment.</x:v>
+        <x:v>Deploy {KeyWord:Public Safety C-UAS} for police, urban security and emergency response.</x:v>
       </x:c>
       <x:c r="AA26" t="str">
         <x:v>Plan {KeyWord:Public Safety C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3302,7 +3302,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K27" t="str">
         <x:v>{KeyWord:Prison C-UAS}</x:v>
@@ -3341,7 +3341,7 @@
         <x:v>{KeyWord:Prison C-UAS} Security</x:v>
       </x:c>
       <x:c r="W27" t="str">
-        <x:v>{KeyWord:Prison C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Prison C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X27" t="str">
         <x:v>{KeyWord:Prison C-UAS} Detection</x:v>
@@ -3350,7 +3350,7 @@
         <x:v>{KeyWord:Prison C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z27" t="str">
-        <x:v>Use {KeyWord:Prison C-UAS} to detect contraband delivery risks and perimeter intrusion.</x:v>
+        <x:v>Deploy {KeyWord:Prison C-UAS} for prison perimeter and contraband drone detection.</x:v>
       </x:c>
       <x:c r="AA27" t="str">
         <x:v>Plan {KeyWord:Prison C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3417,7 +3417,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K28" t="str">
         <x:v>{KeyWord:Port Security C-UAS}</x:v>
@@ -3456,7 +3456,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Security</x:v>
       </x:c>
       <x:c r="W28" t="str">
-        <x:v>{KeyWord:Port Security C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Port Security C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X28" t="str">
         <x:v>{KeyWord:Port Security C-UAS} Detection</x:v>
@@ -3465,7 +3465,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z28" t="str">
-        <x:v>Use {KeyWord:Port Security C-UAS} to monitor cargo, logistics and unauthorized aerial surveillance.</x:v>
+        <x:v>Deploy {KeyWord:Port Security C-UAS} for ports, cargo terminals and logistics security.</x:v>
       </x:c>
       <x:c r="AA28" t="str">
         <x:v>Plan {KeyWord:Port Security C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3499,7 +3499,7 @@
         <x:v>port-security</x:v>
       </x:c>
       <x:c r="AX28" t="str">
-        <x:v>drone-monitor</x:v>
+        <x:v>drone-system</x:v>
       </x:c>
       <x:c r="AY28" t="str">
         <x:v>https://n-tet.com/solutions/low-altitude-airspace-monitoring</x:v>
@@ -3532,7 +3532,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K29" t="str">
         <x:v>{KeyWord:Mass Event C-UAS}</x:v>
@@ -3571,7 +3571,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Security</x:v>
       </x:c>
       <x:c r="W29" t="str">
-        <x:v>{KeyWord:Mass Event C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Mass Event C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X29" t="str">
         <x:v>{KeyWord:Mass Event C-UAS} Detection</x:v>
@@ -3580,7 +3580,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z29" t="str">
-        <x:v>Use {KeyWord:Mass Event C-UAS} to monitor stadiums, major events and dense crowds.</x:v>
+        <x:v>Deploy {KeyWord:Mass Event C-UAS} for stadiums, concerts and major event security.</x:v>
       </x:c>
       <x:c r="AA29" t="str">
         <x:v>Plan {KeyWord:Mass Event C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3647,7 +3647,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J30" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K30" t="str">
         <x:v>{KeyWord:VIP Property C-UAS}</x:v>
@@ -3686,7 +3686,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Security</x:v>
       </x:c>
       <x:c r="W30" t="str">
-        <x:v>{KeyWord:VIP Property C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:VIP Property C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X30" t="str">
         <x:v>{KeyWord:VIP Property C-UAS} Detection</x:v>
@@ -3695,7 +3695,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z30" t="str">
-        <x:v>Use {KeyWord:VIP Property C-UAS} for convoys, residences and private asset protection.</x:v>
+        <x:v>Deploy {KeyWord:VIP Property C-UAS} for villas, convoys and private estate security.</x:v>
       </x:c>
       <x:c r="AA30" t="str">
         <x:v>Plan {KeyWord:VIP Property C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3762,7 +3762,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K31" t="str">
         <x:v>{KeyWord:Enterprise C-UAS}</x:v>
@@ -3801,7 +3801,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Security</x:v>
       </x:c>
       <x:c r="W31" t="str">
-        <x:v>{KeyWord:Enterprise C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Enterprise C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X31" t="str">
         <x:v>{KeyWord:Enterprise C-UAS} Detection</x:v>
@@ -3810,7 +3810,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z31" t="str">
-        <x:v>Use {KeyWord:Enterprise C-UAS} to monitor headquarters, IP assets and unauthorized filming.</x:v>
+        <x:v>Deploy {KeyWord:Enterprise C-UAS} for mines, refineries and industrial site security.</x:v>
       </x:c>
       <x:c r="AA31" t="str">
         <x:v>Plan {KeyWord:Enterprise C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3877,7 +3877,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K32" t="str">
         <x:v>{KeyWord:Critical Site C-UAS}</x:v>
@@ -3916,7 +3916,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Security</x:v>
       </x:c>
       <x:c r="W32" t="str">
-        <x:v>{KeyWord:Critical Site C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Critical Site C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X32" t="str">
         <x:v>{KeyWord:Critical Site C-UAS} Detection</x:v>
@@ -3925,7 +3925,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z32" t="str">
-        <x:v>Use {KeyWord:Critical Site C-UAS} to monitor critical assets and unauthorized aerial activity.</x:v>
+        <x:v>Deploy {KeyWord:Critical Site C-UAS} for critical facilities and national asset security.</x:v>
       </x:c>
       <x:c r="AA32" t="str">
         <x:v>Plan {KeyWord:Critical Site C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -3992,7 +3992,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K33" t="str">
         <x:v>{KeyWord:Power Plant C-UAS}</x:v>
@@ -4031,7 +4031,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Security</x:v>
       </x:c>
       <x:c r="W33" t="str">
-        <x:v>{KeyWord:Power Plant C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Power Plant C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X33" t="str">
         <x:v>{KeyWord:Power Plant C-UAS} Detection</x:v>
@@ -4040,7 +4040,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z33" t="str">
-        <x:v>Use {KeyWord:Power Plant C-UAS} to monitor power plants, grids and energy sites.</x:v>
+        <x:v>Deploy {KeyWord:Power Plant C-UAS} for power plants, grids and energy site security.</x:v>
       </x:c>
       <x:c r="AA33" t="str">
         <x:v>Plan {KeyWord:Power Plant C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -4107,7 +4107,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K34" t="str">
         <x:v>{KeyWord:Airport C-UAS}</x:v>
@@ -4146,7 +4146,7 @@
         <x:v>{KeyWord:Airport C-UAS} Security</x:v>
       </x:c>
       <x:c r="W34" t="str">
-        <x:v>{KeyWord:Airport C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Airport C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X34" t="str">
         <x:v>{KeyWord:Airport C-UAS} Detection</x:v>
@@ -4155,7 +4155,7 @@
         <x:v>{KeyWord:Airport C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z34" t="str">
-        <x:v>Use {KeyWord:Airport C-UAS} to monitor drone risks near runways and flight operations.</x:v>
+        <x:v>Deploy {KeyWord:Airport C-UAS} for runways, airfields and airport security.</x:v>
       </x:c>
       <x:c r="AA34" t="str">
         <x:v>Plan {KeyWord:Airport C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -4222,7 +4222,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K35" t="str">
         <x:v>{KeyWord:Border C-UAS}</x:v>
@@ -4261,7 +4261,7 @@
         <x:v>{KeyWord:Border C-UAS} Security</x:v>
       </x:c>
       <x:c r="W35" t="str">
-        <x:v>{KeyWord:Border C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Border C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X35" t="str">
         <x:v>{KeyWord:Border C-UAS} Detection</x:v>
@@ -4270,7 +4270,7 @@
         <x:v>{KeyWord:Border C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z35" t="str">
-        <x:v>Use {KeyWord:Border C-UAS} to monitor border posts, patrol routes and unauthorized drones.</x:v>
+        <x:v>Deploy {KeyWord:Border C-UAS} for border posts, checkpoints and patrol routes.</x:v>
       </x:c>
       <x:c r="AA35" t="str">
         <x:v>Plan {KeyWord:Border C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -4337,7 +4337,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J36" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K36" t="str">
         <x:v>{KeyWord:Public Safety C-UAS}</x:v>
@@ -4376,7 +4376,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Security</x:v>
       </x:c>
       <x:c r="W36" t="str">
-        <x:v>{KeyWord:Public Safety C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Public Safety C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X36" t="str">
         <x:v>{KeyWord:Public Safety C-UAS} Detection</x:v>
@@ -4385,7 +4385,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z36" t="str">
-        <x:v>Use {KeyWord:Public Safety C-UAS} for law enforcement, urban events and emergency deployment.</x:v>
+        <x:v>Deploy {KeyWord:Public Safety C-UAS} for police, urban security and emergency response.</x:v>
       </x:c>
       <x:c r="AA36" t="str">
         <x:v>Plan {KeyWord:Public Safety C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -4452,7 +4452,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K37" t="str">
         <x:v>{KeyWord:Prison C-UAS}</x:v>
@@ -4491,7 +4491,7 @@
         <x:v>{KeyWord:Prison C-UAS} Security</x:v>
       </x:c>
       <x:c r="W37" t="str">
-        <x:v>{KeyWord:Prison C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Prison C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X37" t="str">
         <x:v>{KeyWord:Prison C-UAS} Detection</x:v>
@@ -4500,7 +4500,7 @@
         <x:v>{KeyWord:Prison C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z37" t="str">
-        <x:v>Use {KeyWord:Prison C-UAS} to detect contraband delivery risks and perimeter intrusion.</x:v>
+        <x:v>Deploy {KeyWord:Prison C-UAS} for prison perimeter and contraband drone detection.</x:v>
       </x:c>
       <x:c r="AA37" t="str">
         <x:v>Plan {KeyWord:Prison C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -4567,7 +4567,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K38" t="str">
         <x:v>{KeyWord:Port Security C-UAS}</x:v>
@@ -4606,7 +4606,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Security</x:v>
       </x:c>
       <x:c r="W38" t="str">
-        <x:v>{KeyWord:Port Security C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Port Security C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X38" t="str">
         <x:v>{KeyWord:Port Security C-UAS} Detection</x:v>
@@ -4615,7 +4615,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z38" t="str">
-        <x:v>Use {KeyWord:Port Security C-UAS} to monitor cargo, logistics and unauthorized aerial surveillance.</x:v>
+        <x:v>Deploy {KeyWord:Port Security C-UAS} for ports, cargo terminals and logistics security.</x:v>
       </x:c>
       <x:c r="AA38" t="str">
         <x:v>Plan {KeyWord:Port Security C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -4649,7 +4649,7 @@
         <x:v>port-security</x:v>
       </x:c>
       <x:c r="AX38" t="str">
-        <x:v>drone-monitor</x:v>
+        <x:v>drone-system</x:v>
       </x:c>
       <x:c r="AY38" t="str">
         <x:v>https://n-tet.com/solutions/low-altitude-airspace-monitoring</x:v>
@@ -4682,7 +4682,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K39" t="str">
         <x:v>{KeyWord:Mass Event C-UAS}</x:v>
@@ -4721,7 +4721,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Security</x:v>
       </x:c>
       <x:c r="W39" t="str">
-        <x:v>{KeyWord:Mass Event C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Mass Event C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X39" t="str">
         <x:v>{KeyWord:Mass Event C-UAS} Detection</x:v>
@@ -4730,7 +4730,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z39" t="str">
-        <x:v>Use {KeyWord:Mass Event C-UAS} to monitor stadiums, major events and dense crowds.</x:v>
+        <x:v>Deploy {KeyWord:Mass Event C-UAS} for stadiums, concerts and major event security.</x:v>
       </x:c>
       <x:c r="AA39" t="str">
         <x:v>Plan {KeyWord:Mass Event C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -4797,7 +4797,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J40" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K40" t="str">
         <x:v>{KeyWord:VIP Property C-UAS}</x:v>
@@ -4836,7 +4836,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Security</x:v>
       </x:c>
       <x:c r="W40" t="str">
-        <x:v>{KeyWord:VIP Property C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:VIP Property C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X40" t="str">
         <x:v>{KeyWord:VIP Property C-UAS} Detection</x:v>
@@ -4845,7 +4845,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z40" t="str">
-        <x:v>Use {KeyWord:VIP Property C-UAS} for convoys, residences and private asset protection.</x:v>
+        <x:v>Deploy {KeyWord:VIP Property C-UAS} for villas, convoys and private estate security.</x:v>
       </x:c>
       <x:c r="AA40" t="str">
         <x:v>Plan {KeyWord:VIP Property C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -4912,7 +4912,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K41" t="str">
         <x:v>{KeyWord:Enterprise C-UAS}</x:v>
@@ -4951,7 +4951,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Security</x:v>
       </x:c>
       <x:c r="W41" t="str">
-        <x:v>{KeyWord:Enterprise C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Enterprise C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X41" t="str">
         <x:v>{KeyWord:Enterprise C-UAS} Detection</x:v>
@@ -4960,7 +4960,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z41" t="str">
-        <x:v>Use {KeyWord:Enterprise C-UAS} to monitor headquarters, IP assets and unauthorized filming.</x:v>
+        <x:v>Deploy {KeyWord:Enterprise C-UAS} for mines, refineries and industrial site security.</x:v>
       </x:c>
       <x:c r="AA41" t="str">
         <x:v>Plan {KeyWord:Enterprise C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5027,7 +5027,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J42" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K42" t="str">
         <x:v>{KeyWord:Critical Site C-UAS}</x:v>
@@ -5066,7 +5066,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Security</x:v>
       </x:c>
       <x:c r="W42" t="str">
-        <x:v>{KeyWord:Critical Site C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Critical Site C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X42" t="str">
         <x:v>{KeyWord:Critical Site C-UAS} Detection</x:v>
@@ -5075,7 +5075,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z42" t="str">
-        <x:v>Use {KeyWord:Critical Site C-UAS} to monitor critical assets and unauthorized aerial activity.</x:v>
+        <x:v>Deploy {KeyWord:Critical Site C-UAS} for critical facilities and national asset security.</x:v>
       </x:c>
       <x:c r="AA42" t="str">
         <x:v>Plan {KeyWord:Critical Site C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5142,7 +5142,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J43" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K43" t="str">
         <x:v>{KeyWord:Power Plant C-UAS}</x:v>
@@ -5181,7 +5181,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Security</x:v>
       </x:c>
       <x:c r="W43" t="str">
-        <x:v>{KeyWord:Power Plant C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Power Plant C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X43" t="str">
         <x:v>{KeyWord:Power Plant C-UAS} Detection</x:v>
@@ -5190,7 +5190,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z43" t="str">
-        <x:v>Use {KeyWord:Power Plant C-UAS} to monitor power plants, grids and energy sites.</x:v>
+        <x:v>Deploy {KeyWord:Power Plant C-UAS} for power plants, grids and energy site security.</x:v>
       </x:c>
       <x:c r="AA43" t="str">
         <x:v>Plan {KeyWord:Power Plant C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5257,7 +5257,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J44" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K44" t="str">
         <x:v>{KeyWord:Airport C-UAS}</x:v>
@@ -5296,7 +5296,7 @@
         <x:v>{KeyWord:Airport C-UAS} Security</x:v>
       </x:c>
       <x:c r="W44" t="str">
-        <x:v>{KeyWord:Airport C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Airport C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X44" t="str">
         <x:v>{KeyWord:Airport C-UAS} Detection</x:v>
@@ -5305,7 +5305,7 @@
         <x:v>{KeyWord:Airport C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z44" t="str">
-        <x:v>Use {KeyWord:Airport C-UAS} to monitor drone risks near runways and flight operations.</x:v>
+        <x:v>Deploy {KeyWord:Airport C-UAS} for runways, airfields and airport security.</x:v>
       </x:c>
       <x:c r="AA44" t="str">
         <x:v>Plan {KeyWord:Airport C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5372,7 +5372,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J45" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K45" t="str">
         <x:v>{KeyWord:Border C-UAS}</x:v>
@@ -5411,7 +5411,7 @@
         <x:v>{KeyWord:Border C-UAS} Security</x:v>
       </x:c>
       <x:c r="W45" t="str">
-        <x:v>{KeyWord:Border C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Border C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X45" t="str">
         <x:v>{KeyWord:Border C-UAS} Detection</x:v>
@@ -5420,7 +5420,7 @@
         <x:v>{KeyWord:Border C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z45" t="str">
-        <x:v>Use {KeyWord:Border C-UAS} to monitor border posts, patrol routes and unauthorized drones.</x:v>
+        <x:v>Deploy {KeyWord:Border C-UAS} for border posts, checkpoints and patrol routes.</x:v>
       </x:c>
       <x:c r="AA45" t="str">
         <x:v>Plan {KeyWord:Border C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5487,7 +5487,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J46" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K46" t="str">
         <x:v>{KeyWord:Public Safety C-UAS}</x:v>
@@ -5526,7 +5526,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Security</x:v>
       </x:c>
       <x:c r="W46" t="str">
-        <x:v>{KeyWord:Public Safety C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Public Safety C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X46" t="str">
         <x:v>{KeyWord:Public Safety C-UAS} Detection</x:v>
@@ -5535,7 +5535,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z46" t="str">
-        <x:v>Use {KeyWord:Public Safety C-UAS} for law enforcement, urban events and emergency deployment.</x:v>
+        <x:v>Deploy {KeyWord:Public Safety C-UAS} for police, urban security and emergency response.</x:v>
       </x:c>
       <x:c r="AA46" t="str">
         <x:v>Plan {KeyWord:Public Safety C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5602,7 +5602,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J47" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K47" t="str">
         <x:v>{KeyWord:Prison C-UAS}</x:v>
@@ -5641,7 +5641,7 @@
         <x:v>{KeyWord:Prison C-UAS} Security</x:v>
       </x:c>
       <x:c r="W47" t="str">
-        <x:v>{KeyWord:Prison C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Prison C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X47" t="str">
         <x:v>{KeyWord:Prison C-UAS} Detection</x:v>
@@ -5650,7 +5650,7 @@
         <x:v>{KeyWord:Prison C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z47" t="str">
-        <x:v>Use {KeyWord:Prison C-UAS} to detect contraband delivery risks and perimeter intrusion.</x:v>
+        <x:v>Deploy {KeyWord:Prison C-UAS} for prison perimeter and contraband drone detection.</x:v>
       </x:c>
       <x:c r="AA47" t="str">
         <x:v>Plan {KeyWord:Prison C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5717,7 +5717,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J48" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K48" t="str">
         <x:v>{KeyWord:Port Security C-UAS}</x:v>
@@ -5756,7 +5756,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Security</x:v>
       </x:c>
       <x:c r="W48" t="str">
-        <x:v>{KeyWord:Port Security C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Port Security C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X48" t="str">
         <x:v>{KeyWord:Port Security C-UAS} Detection</x:v>
@@ -5765,7 +5765,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z48" t="str">
-        <x:v>Use {KeyWord:Port Security C-UAS} to monitor cargo, logistics and unauthorized aerial surveillance.</x:v>
+        <x:v>Deploy {KeyWord:Port Security C-UAS} for ports, cargo terminals and logistics security.</x:v>
       </x:c>
       <x:c r="AA48" t="str">
         <x:v>Plan {KeyWord:Port Security C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>port-security</x:v>
       </x:c>
       <x:c r="AX48" t="str">
-        <x:v>drone-monitor</x:v>
+        <x:v>drone-system</x:v>
       </x:c>
       <x:c r="AY48" t="str">
         <x:v>https://n-tet.com/solutions/low-altitude-airspace-monitoring</x:v>
@@ -5832,7 +5832,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J49" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K49" t="str">
         <x:v>{KeyWord:Mass Event C-UAS}</x:v>
@@ -5871,7 +5871,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Security</x:v>
       </x:c>
       <x:c r="W49" t="str">
-        <x:v>{KeyWord:Mass Event C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Mass Event C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X49" t="str">
         <x:v>{KeyWord:Mass Event C-UAS} Detection</x:v>
@@ -5880,7 +5880,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z49" t="str">
-        <x:v>Use {KeyWord:Mass Event C-UAS} to monitor stadiums, major events and dense crowds.</x:v>
+        <x:v>Deploy {KeyWord:Mass Event C-UAS} for stadiums, concerts and major event security.</x:v>
       </x:c>
       <x:c r="AA49" t="str">
         <x:v>Plan {KeyWord:Mass Event C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -5947,7 +5947,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J50" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K50" t="str">
         <x:v>{KeyWord:VIP Property C-UAS}</x:v>
@@ -5986,7 +5986,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Security</x:v>
       </x:c>
       <x:c r="W50" t="str">
-        <x:v>{KeyWord:VIP Property C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:VIP Property C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X50" t="str">
         <x:v>{KeyWord:VIP Property C-UAS} Detection</x:v>
@@ -5995,7 +5995,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z50" t="str">
-        <x:v>Use {KeyWord:VIP Property C-UAS} for convoys, residences and private asset protection.</x:v>
+        <x:v>Deploy {KeyWord:VIP Property C-UAS} for villas, convoys and private estate security.</x:v>
       </x:c>
       <x:c r="AA50" t="str">
         <x:v>Plan {KeyWord:VIP Property C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6062,7 +6062,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K51" t="str">
         <x:v>{KeyWord:Enterprise C-UAS}</x:v>
@@ -6101,7 +6101,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Security</x:v>
       </x:c>
       <x:c r="W51" t="str">
-        <x:v>{KeyWord:Enterprise C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Enterprise C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X51" t="str">
         <x:v>{KeyWord:Enterprise C-UAS} Detection</x:v>
@@ -6110,7 +6110,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z51" t="str">
-        <x:v>Use {KeyWord:Enterprise C-UAS} to monitor headquarters, IP assets and unauthorized filming.</x:v>
+        <x:v>Deploy {KeyWord:Enterprise C-UAS} for mines, refineries and industrial site security.</x:v>
       </x:c>
       <x:c r="AA51" t="str">
         <x:v>Plan {KeyWord:Enterprise C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6177,7 +6177,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J52" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K52" t="str">
         <x:v>{KeyWord:Critical Site C-UAS}</x:v>
@@ -6216,7 +6216,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Security</x:v>
       </x:c>
       <x:c r="W52" t="str">
-        <x:v>{KeyWord:Critical Site C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Critical Site C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X52" t="str">
         <x:v>{KeyWord:Critical Site C-UAS} Detection</x:v>
@@ -6225,7 +6225,7 @@
         <x:v>{KeyWord:Critical Site C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z52" t="str">
-        <x:v>Use {KeyWord:Critical Site C-UAS} to monitor critical assets and unauthorized aerial activity.</x:v>
+        <x:v>Deploy {KeyWord:Critical Site C-UAS} for critical facilities and national asset security.</x:v>
       </x:c>
       <x:c r="AA52" t="str">
         <x:v>Plan {KeyWord:Critical Site C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6292,7 +6292,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J53" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K53" t="str">
         <x:v>{KeyWord:Power Plant C-UAS}</x:v>
@@ -6331,7 +6331,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Security</x:v>
       </x:c>
       <x:c r="W53" t="str">
-        <x:v>{KeyWord:Power Plant C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Power Plant C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X53" t="str">
         <x:v>{KeyWord:Power Plant C-UAS} Detection</x:v>
@@ -6340,7 +6340,7 @@
         <x:v>{KeyWord:Power Plant C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z53" t="str">
-        <x:v>Use {KeyWord:Power Plant C-UAS} to monitor power plants, grids and energy sites.</x:v>
+        <x:v>Deploy {KeyWord:Power Plant C-UAS} for power plants, grids and energy site security.</x:v>
       </x:c>
       <x:c r="AA53" t="str">
         <x:v>Plan {KeyWord:Power Plant C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6407,7 +6407,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J54" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K54" t="str">
         <x:v>{KeyWord:Airport C-UAS}</x:v>
@@ -6446,7 +6446,7 @@
         <x:v>{KeyWord:Airport C-UAS} Security</x:v>
       </x:c>
       <x:c r="W54" t="str">
-        <x:v>{KeyWord:Airport C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Airport C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X54" t="str">
         <x:v>{KeyWord:Airport C-UAS} Detection</x:v>
@@ -6455,7 +6455,7 @@
         <x:v>{KeyWord:Airport C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z54" t="str">
-        <x:v>Use {KeyWord:Airport C-UAS} to monitor drone risks near runways and flight operations.</x:v>
+        <x:v>Deploy {KeyWord:Airport C-UAS} for runways, airfields and airport security.</x:v>
       </x:c>
       <x:c r="AA54" t="str">
         <x:v>Plan {KeyWord:Airport C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6522,7 +6522,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J55" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K55" t="str">
         <x:v>{KeyWord:Border C-UAS}</x:v>
@@ -6561,7 +6561,7 @@
         <x:v>{KeyWord:Border C-UAS} Security</x:v>
       </x:c>
       <x:c r="W55" t="str">
-        <x:v>{KeyWord:Border C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Border C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X55" t="str">
         <x:v>{KeyWord:Border C-UAS} Detection</x:v>
@@ -6570,7 +6570,7 @@
         <x:v>{KeyWord:Border C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z55" t="str">
-        <x:v>Use {KeyWord:Border C-UAS} to monitor border posts, patrol routes and unauthorized drones.</x:v>
+        <x:v>Deploy {KeyWord:Border C-UAS} for border posts, checkpoints and patrol routes.</x:v>
       </x:c>
       <x:c r="AA55" t="str">
         <x:v>Plan {KeyWord:Border C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6637,7 +6637,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J56" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K56" t="str">
         <x:v>{KeyWord:Public Safety C-UAS}</x:v>
@@ -6676,7 +6676,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Security</x:v>
       </x:c>
       <x:c r="W56" t="str">
-        <x:v>{KeyWord:Public Safety C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Public Safety C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X56" t="str">
         <x:v>{KeyWord:Public Safety C-UAS} Detection</x:v>
@@ -6685,7 +6685,7 @@
         <x:v>{KeyWord:Public Safety C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z56" t="str">
-        <x:v>Use {KeyWord:Public Safety C-UAS} for law enforcement, urban events and emergency deployment.</x:v>
+        <x:v>Deploy {KeyWord:Public Safety C-UAS} for police, urban security and emergency response.</x:v>
       </x:c>
       <x:c r="AA56" t="str">
         <x:v>Plan {KeyWord:Public Safety C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6752,7 +6752,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J57" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K57" t="str">
         <x:v>{KeyWord:Prison C-UAS}</x:v>
@@ -6791,7 +6791,7 @@
         <x:v>{KeyWord:Prison C-UAS} Security</x:v>
       </x:c>
       <x:c r="W57" t="str">
-        <x:v>{KeyWord:Prison C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Prison C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X57" t="str">
         <x:v>{KeyWord:Prison C-UAS} Detection</x:v>
@@ -6800,7 +6800,7 @@
         <x:v>{KeyWord:Prison C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z57" t="str">
-        <x:v>Use {KeyWord:Prison C-UAS} to detect contraband delivery risks and perimeter intrusion.</x:v>
+        <x:v>Deploy {KeyWord:Prison C-UAS} for prison perimeter and contraband drone detection.</x:v>
       </x:c>
       <x:c r="AA57" t="str">
         <x:v>Plan {KeyWord:Prison C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6867,7 +6867,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J58" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K58" t="str">
         <x:v>{KeyWord:Port Security C-UAS}</x:v>
@@ -6906,7 +6906,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Security</x:v>
       </x:c>
       <x:c r="W58" t="str">
-        <x:v>{KeyWord:Port Security C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Port Security C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X58" t="str">
         <x:v>{KeyWord:Port Security C-UAS} Detection</x:v>
@@ -6915,7 +6915,7 @@
         <x:v>{KeyWord:Port Security C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z58" t="str">
-        <x:v>Use {KeyWord:Port Security C-UAS} to monitor cargo, logistics and unauthorized aerial surveillance.</x:v>
+        <x:v>Deploy {KeyWord:Port Security C-UAS} for ports, cargo terminals and logistics security.</x:v>
       </x:c>
       <x:c r="AA58" t="str">
         <x:v>Plan {KeyWord:Port Security C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -6949,7 +6949,7 @@
         <x:v>port-security</x:v>
       </x:c>
       <x:c r="AX58" t="str">
-        <x:v>drone-monitor</x:v>
+        <x:v>drone-system</x:v>
       </x:c>
       <x:c r="AY58" t="str">
         <x:v>https://n-tet.com/solutions/low-altitude-airspace-monitoring</x:v>
@@ -6982,7 +6982,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J59" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K59" t="str">
         <x:v>{KeyWord:Mass Event C-UAS}</x:v>
@@ -7021,7 +7021,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Security</x:v>
       </x:c>
       <x:c r="W59" t="str">
-        <x:v>{KeyWord:Mass Event C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Mass Event C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X59" t="str">
         <x:v>{KeyWord:Mass Event C-UAS} Detection</x:v>
@@ -7030,7 +7030,7 @@
         <x:v>{KeyWord:Mass Event C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z59" t="str">
-        <x:v>Use {KeyWord:Mass Event C-UAS} to monitor stadiums, major events and dense crowds.</x:v>
+        <x:v>Deploy {KeyWord:Mass Event C-UAS} for stadiums, concerts and major event security.</x:v>
       </x:c>
       <x:c r="AA59" t="str">
         <x:v>Plan {KeyWord:Mass Event C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -7097,7 +7097,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J60" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K60" t="str">
         <x:v>{KeyWord:VIP Property C-UAS}</x:v>
@@ -7136,7 +7136,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Security</x:v>
       </x:c>
       <x:c r="W60" t="str">
-        <x:v>{KeyWord:VIP Property C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:VIP Property C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X60" t="str">
         <x:v>{KeyWord:VIP Property C-UAS} Detection</x:v>
@@ -7145,7 +7145,7 @@
         <x:v>{KeyWord:VIP Property C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z60" t="str">
-        <x:v>Use {KeyWord:VIP Property C-UAS} for convoys, residences and private asset protection.</x:v>
+        <x:v>Deploy {KeyWord:VIP Property C-UAS} for villas, convoys and private estate security.</x:v>
       </x:c>
       <x:c r="AA60" t="str">
         <x:v>Plan {KeyWord:VIP Property C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
@@ -7212,7 +7212,7 @@
         <x:v>Responsive search ad</x:v>
       </x:c>
       <x:c r="J61" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="K61" t="str">
         <x:v>{KeyWord:Enterprise C-UAS}</x:v>
@@ -7251,7 +7251,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Security</x:v>
       </x:c>
       <x:c r="W61" t="str">
-        <x:v>{KeyWord:Enterprise C-UAS} Monitoring</x:v>
+        <x:v>{KeyWord:Enterprise C-UAS} Equipment</x:v>
       </x:c>
       <x:c r="X61" t="str">
         <x:v>{KeyWord:Enterprise C-UAS} Detection</x:v>
@@ -7260,7 +7260,7 @@
         <x:v>{KeyWord:Enterprise C-UAS} Supplier</x:v>
       </x:c>
       <x:c r="Z61" t="str">
-        <x:v>Use {KeyWord:Enterprise C-UAS} to monitor headquarters, IP assets and unauthorized filming.</x:v>
+        <x:v>Deploy {KeyWord:Enterprise C-UAS} for mines, refineries and industrial site security.</x:v>
       </x:c>
       <x:c r="AA61" t="str">
         <x:v>Plan {KeyWord:Enterprise C-UAS} coverage for fixed sites, portable teams and vehicles.</x:v>
